--- a/题库/PY程序设计模拟题4.xlsx
+++ b/题库/PY程序设计模拟题4.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="129">
   <si>
     <t>题号</t>
   </si>
@@ -103,6 +103,9 @@
     <t>语句x=input()执行时，如果从键盘输入12并按回车键，则x的值是（）。</t>
   </si>
   <si>
+    <t>le2</t>
+  </si>
+  <si>
     <t>'12'</t>
   </si>
   <si>
@@ -169,7 +172,73 @@
     <t>key</t>
   </si>
   <si>
-    <t>下列语句执行后的结果是（）。</t>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下列语句执行后的结果是（）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+d1 = {1: "food"}
+d2 = {1: "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>食品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>", 2: "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>饮料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"}
+d1.update(d2)
+print(d1[1])</t>
+    </r>
   </si>
   <si>
     <t>食品</t>
@@ -181,18 +250,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>d1={1:"food"}</t>
-  </si>
-  <si>
-    <t>d2={1:"食品", 2:"饮料"}</t>
-  </si>
-  <si>
-    <t>d1.update(d2)</t>
-  </si>
-  <si>
-    <t>print(d1[1])</t>
-  </si>
-  <si>
     <t>欲将两数中较小的数返回，应定义的匿名函数为（）。</t>
   </si>
   <si>
@@ -223,7 +280,56 @@
     <t>x += y</t>
   </si>
   <si>
-    <t>下面代码的输出结果为()。</t>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下面代码的输出结果为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+d = {}
+for i in range(26):
+    d[chr(i+ord("A"))] = chr((i+13)%26+ord("A"))
+for c in "Python":
+    print(d.get(c,c),end="")</t>
+    </r>
   </si>
   <si>
     <t>Plguba</t>
@@ -238,22 +344,35 @@
     <t>Cython</t>
   </si>
   <si>
-    <t>d={}</t>
-  </si>
-  <si>
-    <t>for i in range(26):</t>
-  </si>
-  <si>
-    <t>d[chr(i+ord("A"))] = chr((i+13)%26+ord("A"))</t>
-  </si>
-  <si>
-    <t>for c in "Python":</t>
-  </si>
-  <si>
-    <t>print(d.get(c,c),end="")</t>
-  </si>
-  <si>
-    <t>下面代码的输出结果是（）。</t>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下面代码的输出结果是（）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+for i in "Python":
+    print(i,end=" ")</t>
+    </r>
   </si>
   <si>
     <t>P, y, t, h, o, n,</t>
@@ -262,12 +381,6 @@
     <t>P y t h o n</t>
   </si>
   <si>
-    <t>for i in "Python":</t>
-  </si>
-  <si>
-    <t>print(i,end=" ")</t>
-  </si>
-  <si>
     <t>下列Python数据中，其元素可以改变的是（）。</t>
   </si>
   <si>
@@ -283,18 +396,14 @@
     <t>数组</t>
   </si>
   <si>
-    <t>当键盘输入“3”的时候，以下程序的输出结果是：</t>
+    <t># 当键盘输入“3”的时候，以下程序的输出结果是：
+r = input("请输入半径：")
+ar = 3.1415 * r * r</t>
   </si>
   <si>
     <t>Type Error</t>
   </si>
   <si>
-    <t>r = input("请输入半径：")</t>
-  </si>
-  <si>
-    <t>ar = 3.1415 * r * r</t>
-  </si>
-  <si>
     <t>以下选项描述正确的是（）。</t>
   </si>
   <si>
@@ -349,16 +458,48 @@
     <t>集合s={1,2,3,4}，执行s.remove(3)后，s的元素个数为【1】。</t>
   </si>
   <si>
-    <t>下列语句的运行结果是【1】。</t>
-  </si>
-  <si>
-    <t>s=[1,2,3,4]</t>
-  </si>
-  <si>
-    <t>s.append([5,6])</t>
-  </si>
-  <si>
-    <t>print(len(s))</t>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下列语句的运行结果是【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+s = [1,2,3,4]
+s.append([5,6])
+print(len(s))</t>
+    </r>
   </si>
   <si>
     <t>表达式'apple.peach,banana,pear'.find('p')的值为【1】。</t>
@@ -794,11 +935,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -810,6 +952,12 @@
     </font>
     <font>
       <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
@@ -963,12 +1111,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1349,137 +1491,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1489,10 +1631,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -1849,7 +2015,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1865,7 +2031,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" ht="92" spans="1:10">
       <c r="A3" s="2">
@@ -1895,7 +2061,7 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" ht="133" spans="1:10">
       <c r="A4" s="2">
@@ -1925,7 +2091,7 @@
       <c r="I4" s="2">
         <v>2</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" ht="155" spans="1:10">
       <c r="A5" s="2">
@@ -1940,22 +2106,22 @@
       <c r="D5" s="2">
         <v>12</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>12</v>
       </c>
-      <c r="F5" s="3">
-        <v>100</v>
+      <c r="F5" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="5"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" ht="101.5" spans="1:10">
       <c r="A6" s="2">
@@ -1965,19 +2131,19 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
@@ -1985,7 +2151,7 @@
       <c r="I6" s="2">
         <v>2</v>
       </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" ht="72.5" spans="1:10">
       <c r="A7" s="2">
@@ -1995,19 +2161,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>16</v>
@@ -2015,7 +2181,7 @@
       <c r="I7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="5"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" ht="72.5" spans="1:10">
       <c r="A8" s="2">
@@ -2025,27 +2191,27 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" ht="106.5" spans="1:10">
       <c r="A9" s="2">
@@ -2055,19 +2221,19 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
@@ -2075,7 +2241,7 @@
       <c r="I9" s="2">
         <v>2</v>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" ht="58" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -2084,8 +2250,8 @@
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -2094,74 +2260,66 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="2">
         <v>2</v>
       </c>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" ht="34" spans="1:10">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="C11" s="6"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" ht="51" spans="1:10">
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="C12" s="6"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" ht="34" spans="1:10">
+      <c r="J12" s="15"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="C13" s="6"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" ht="34" spans="1:10">
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="C14" s="7"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="8"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" ht="87" spans="1:10">
       <c r="A15" s="2">
@@ -2171,19 +2329,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -2191,7 +2349,7 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="5"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" ht="75" spans="1:10">
       <c r="A16" s="2">
@@ -2201,19 +2359,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>22</v>
@@ -2221,7 +2379,7 @@
       <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:10">
       <c r="A17" s="2">
@@ -2230,98 +2388,88 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="2">
         <v>2</v>
       </c>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" ht="17" spans="1:10">
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="C18" s="6"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" ht="51" spans="1:10">
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="C19" s="6"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" ht="119" spans="1:10">
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="C20" s="6"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="5"/>
-    </row>
-    <row r="21" ht="51" spans="1:10">
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="C21" s="6"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="5"/>
-    </row>
-    <row r="22" ht="51" spans="1:10">
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="C22" s="7"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="5"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" ht="58" customHeight="1" spans="1:10">
       <c r="A23" s="2">
@@ -2330,20 +2478,20 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>74</v>
+      <c r="C23" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>16</v>
@@ -2351,35 +2499,31 @@
       <c r="I23" s="2">
         <v>2</v>
       </c>
-      <c r="J23" s="5"/>
-    </row>
-    <row r="24" ht="51" spans="1:10">
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="5"/>
-    </row>
-    <row r="25" ht="34" spans="1:10">
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="5"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" ht="89.5" spans="1:10">
       <c r="A26" s="2">
@@ -2389,19 +2533,19 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>16</v>
@@ -2409,7 +2553,7 @@
       <c r="I26" s="2">
         <v>2</v>
       </c>
-      <c r="J26" s="5"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" ht="89.5" customHeight="1" spans="1:10">
       <c r="A27" s="2">
@@ -2418,8 +2562,8 @@
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>84</v>
+      <c r="C27" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="D27" s="2">
         <v>29</v>
@@ -2428,46 +2572,42 @@
         <v>28</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G27" s="2">
         <v>28.27</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I27" s="2">
         <v>2</v>
       </c>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" ht="65.5" spans="1:10">
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="C28" s="6"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="5"/>
-    </row>
-    <row r="29" ht="51" spans="1:10">
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="C29" s="7"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="5"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" ht="94.5" spans="1:10">
       <c r="A30" s="2">
@@ -2477,19 +2617,19 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -2497,11 +2637,11 @@
       <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="5"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" ht="17" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2511,17 +2651,17 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="5"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" ht="97" spans="1:10">
       <c r="A32" s="2">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2533,127 +2673,127 @@
       <c r="I32" s="2">
         <v>2</v>
       </c>
-      <c r="J32" s="5"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" ht="121" spans="1:10">
       <c r="A33" s="2">
         <v>17</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I33" s="2">
         <v>2</v>
       </c>
-      <c r="J33" s="5"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" ht="114" spans="1:10">
       <c r="A34" s="2">
         <v>18</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I34" s="2">
         <v>2</v>
       </c>
-      <c r="J34" s="5"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" ht="147.5" spans="1:10">
       <c r="A35" s="2">
         <v>19</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="I35" s="2">
         <v>2</v>
       </c>
-      <c r="J35" s="5"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" ht="63" spans="1:10">
       <c r="A36" s="2">
         <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I36" s="2">
         <v>2</v>
       </c>
-      <c r="J36" s="5"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" ht="111.5" spans="1:10">
       <c r="A37" s="2">
         <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I37" s="2">
         <v>2</v>
       </c>
-      <c r="J37" s="5"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" ht="128.5" spans="1:10">
       <c r="A38" s="2">
         <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2665,17 +2805,17 @@
       <c r="I38" s="2">
         <v>2</v>
       </c>
-      <c r="J38" s="5"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" ht="60.5" customHeight="1" spans="1:10">
       <c r="A39" s="2">
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2687,59 +2827,53 @@
       <c r="I39" s="2">
         <v>2</v>
       </c>
-      <c r="J39" s="5"/>
-    </row>
-    <row r="40" ht="34" spans="1:10">
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="C40" s="10"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="5"/>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" ht="34" spans="1:10">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="2" t="s">
-        <v>108</v>
-      </c>
+      <c r="C41" s="10"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="5"/>
+      <c r="J41" s="13"/>
     </row>
     <row r="42" ht="34" spans="1:10">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="C42" s="11"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="5"/>
+      <c r="J42" s="13"/>
     </row>
     <row r="43" ht="114" spans="1:10">
       <c r="A43" s="2">
         <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2751,39 +2885,39 @@
       <c r="I43" s="2">
         <v>2</v>
       </c>
-      <c r="J43" s="5"/>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" ht="135.5" spans="1:10">
       <c r="A44" s="2">
         <v>25</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="I44" s="2">
         <v>2</v>
       </c>
-      <c r="J44" s="5"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" ht="80" spans="1:10">
       <c r="A45" s="2">
         <v>26</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -2795,39 +2929,39 @@
       <c r="I45" s="2">
         <v>2</v>
       </c>
-      <c r="J45" s="5"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46" ht="114" spans="1:10">
       <c r="A46" s="2">
         <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
       </c>
-      <c r="J46" s="5"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" ht="131" spans="1:10">
       <c r="A47" s="2">
         <v>28</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2839,39 +2973,39 @@
       <c r="I47" s="2">
         <v>2</v>
       </c>
-      <c r="J47" s="5"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" ht="164.5" spans="1:10">
       <c r="A48" s="2">
         <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="I48" s="2">
         <v>2</v>
       </c>
-      <c r="J48" s="5"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" ht="111.5" spans="1:10">
       <c r="A49" s="2">
         <v>30</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -2883,11 +3017,11 @@
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="5"/>
+      <c r="J49" s="13"/>
     </row>
     <row r="50" ht="17" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2897,23 +3031,23 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="5"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" ht="116" spans="1:10">
       <c r="A51" s="2">
         <v>31</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2923,23 +3057,23 @@
       <c r="I51" s="2">
         <v>1</v>
       </c>
-      <c r="J51" s="5"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52" ht="114" spans="1:10">
       <c r="A52" s="2">
         <v>32</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -2949,23 +3083,23 @@
       <c r="I52" s="2">
         <v>1</v>
       </c>
-      <c r="J52" s="5"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" ht="89.5" spans="1:10">
       <c r="A53" s="2">
         <v>33</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -2975,23 +3109,23 @@
       <c r="I53" s="2">
         <v>1</v>
       </c>
-      <c r="J53" s="5"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" ht="63" spans="1:10">
       <c r="A54" s="2">
         <v>34</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3001,23 +3135,23 @@
       <c r="I54" s="2">
         <v>1</v>
       </c>
-      <c r="J54" s="5"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" ht="217.5" spans="1:10">
       <c r="A55" s="2">
         <v>35</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3027,23 +3161,23 @@
       <c r="I55" s="2">
         <v>1</v>
       </c>
-      <c r="J55" s="5"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="56" ht="167" spans="1:10">
       <c r="A56" s="2">
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3053,23 +3187,23 @@
       <c r="I56" s="2">
         <v>1</v>
       </c>
-      <c r="J56" s="5"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" ht="177" spans="1:10">
       <c r="A57" s="2">
         <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3079,23 +3213,23 @@
       <c r="I57" s="2">
         <v>1</v>
       </c>
-      <c r="J57" s="5"/>
+      <c r="J57" s="13"/>
     </row>
     <row r="58" ht="92" spans="1:10">
       <c r="A58" s="2">
         <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3105,23 +3239,23 @@
       <c r="I58" s="2">
         <v>1</v>
       </c>
-      <c r="J58" s="5"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" ht="89.5" spans="1:10">
       <c r="A59" s="2">
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -3131,23 +3265,23 @@
       <c r="I59" s="2">
         <v>1</v>
       </c>
-      <c r="J59" s="5"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" ht="75" spans="1:10">
       <c r="A60" s="2">
         <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3157,11 +3291,11 @@
       <c r="I60" s="2">
         <v>1</v>
       </c>
-      <c r="J60" s="5"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61" ht="17" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3171,30 +3305,30 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="5"/>
+      <c r="J61" s="13"/>
     </row>
     <row r="62" ht="87" spans="1:10">
       <c r="A62" s="2">
         <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="4" t="s">
-        <v>135</v>
+      <c r="H62" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="I62" s="2">
         <v>10</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>136</v>
+      <c r="J62" s="13" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="63" ht="119" spans="1:10">
@@ -3202,28 +3336,28 @@
         <v>42</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="4" t="s">
-        <v>138</v>
+      <c r="H63" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="I63" s="2">
         <v>10</v>
       </c>
-      <c r="J63" s="5" t="s">
-        <v>139</v>
+      <c r="J63" s="13" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="64" ht="17" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3233,34 +3367,34 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="5"/>
+      <c r="J64" s="13"/>
     </row>
     <row r="65" ht="409.5" spans="1:10">
       <c r="A65" s="2">
         <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="4" t="s">
-        <v>142</v>
+      <c r="H65" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="I65" s="2">
         <v>10</v>
       </c>
-      <c r="J65" s="5" t="s">
-        <v>143</v>
+      <c r="J65" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="46">
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A23:A25"/>
@@ -3271,6 +3405,11 @@
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C39:C42"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="D23:D25"/>

--- a/题库/PY程序设计模拟题4.xlsx
+++ b/题库/PY程序设计模拟题4.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
   <si>
     <t>题号</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>语句x=input()执行时，如果从键盘输入12并按回车键，则x的值是（）。</t>
+  </si>
+  <si>
+    <t>12.0</t>
   </si>
   <si>
     <t>le2</t>
@@ -459,6 +462,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"># </t>
     </r>
     <r>
@@ -935,12 +944,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1621,7 +1629,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1631,7 +1639,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1647,15 +1655,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2015,7 +2014,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2031,7 +2030,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="13"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" ht="92" spans="1:10">
       <c r="A3" s="2">
@@ -2061,7 +2060,7 @@
       <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="10"/>
     </row>
     <row r="4" ht="133" spans="1:10">
       <c r="A4" s="2">
@@ -2091,7 +2090,7 @@
       <c r="I4" s="2">
         <v>2</v>
       </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="10"/>
     </row>
     <row r="5" ht="155" spans="1:10">
       <c r="A5" s="2">
@@ -2106,22 +2105,22 @@
       <c r="D5" s="2">
         <v>12</v>
       </c>
-      <c r="E5" s="3">
-        <v>12</v>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="13"/>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" ht="101.5" spans="1:10">
       <c r="A6" s="2">
@@ -2131,19 +2130,19 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
@@ -2151,7 +2150,7 @@
       <c r="I6" s="2">
         <v>2</v>
       </c>
-      <c r="J6" s="13"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" ht="72.5" spans="1:10">
       <c r="A7" s="2">
@@ -2161,19 +2160,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>16</v>
@@ -2181,7 +2180,7 @@
       <c r="I7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="13"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" ht="72.5" spans="1:10">
       <c r="A8" s="2">
@@ -2191,27 +2190,27 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
       </c>
-      <c r="J8" s="13"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" ht="106.5" spans="1:10">
       <c r="A9" s="2">
@@ -2221,19 +2220,19 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
@@ -2241,7 +2240,7 @@
       <c r="I9" s="2">
         <v>2</v>
       </c>
-      <c r="J9" s="13"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" ht="58" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -2251,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -2260,18 +2259,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I10" s="2">
         <v>2</v>
       </c>
-      <c r="J10" s="14"/>
+      <c r="J10" s="11"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2"/>
@@ -2283,7 +2282,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="15"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2"/>
@@ -2295,7 +2294,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="15"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2"/>
@@ -2307,7 +2306,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="15"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2"/>
@@ -2319,7 +2318,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="16"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" ht="87" spans="1:10">
       <c r="A15" s="2">
@@ -2329,19 +2328,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -2349,7 +2348,7 @@
       <c r="I15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="13"/>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" ht="75" spans="1:10">
       <c r="A16" s="2">
@@ -2359,19 +2358,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>22</v>
@@ -2379,7 +2378,7 @@
       <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:10">
       <c r="A17" s="2">
@@ -2389,27 +2388,27 @@
         <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I17" s="2">
         <v>2</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2"/>
@@ -2421,7 +2420,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2"/>
@@ -2433,7 +2432,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2"/>
@@ -2445,7 +2444,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2"/>
@@ -2457,7 +2456,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2"/>
@@ -2469,7 +2468,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" ht="58" customHeight="1" spans="1:10">
       <c r="A23" s="2">
@@ -2479,19 +2478,19 @@
         <v>10</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>16</v>
@@ -2499,7 +2498,7 @@
       <c r="I23" s="2">
         <v>2</v>
       </c>
-      <c r="J23" s="13"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2"/>
@@ -2511,7 +2510,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2"/>
@@ -2523,7 +2522,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" ht="89.5" spans="1:10">
       <c r="A26" s="2">
@@ -2533,19 +2532,19 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>16</v>
@@ -2553,7 +2552,7 @@
       <c r="I26" s="2">
         <v>2</v>
       </c>
-      <c r="J26" s="13"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" ht="89.5" customHeight="1" spans="1:10">
       <c r="A27" s="2">
@@ -2563,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2">
         <v>29</v>
@@ -2572,18 +2571,18 @@
         <v>28</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="2">
         <v>28.27</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I27" s="2">
         <v>2</v>
       </c>
-      <c r="J27" s="13"/>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2"/>
@@ -2595,7 +2594,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
+      <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2"/>
@@ -2607,7 +2606,7 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" ht="94.5" spans="1:10">
       <c r="A30" s="2">
@@ -2617,19 +2616,19 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -2637,11 +2636,11 @@
       <c r="I30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="13"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" ht="17" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2651,17 +2650,17 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" ht="97" spans="1:10">
       <c r="A32" s="2">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2673,127 +2672,127 @@
       <c r="I32" s="2">
         <v>2</v>
       </c>
-      <c r="J32" s="13"/>
+      <c r="J32" s="10"/>
     </row>
     <row r="33" ht="121" spans="1:10">
       <c r="A33" s="2">
         <v>17</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" s="2">
         <v>2</v>
       </c>
-      <c r="J33" s="13"/>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" ht="114" spans="1:10">
       <c r="A34" s="2">
         <v>18</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I34" s="2">
         <v>2</v>
       </c>
-      <c r="J34" s="13"/>
+      <c r="J34" s="10"/>
     </row>
     <row r="35" ht="147.5" spans="1:10">
       <c r="A35" s="2">
         <v>19</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I35" s="2">
         <v>2</v>
       </c>
-      <c r="J35" s="13"/>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" ht="63" spans="1:10">
       <c r="A36" s="2">
         <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I36" s="2">
         <v>2</v>
       </c>
-      <c r="J36" s="13"/>
+      <c r="J36" s="10"/>
     </row>
     <row r="37" ht="111.5" spans="1:10">
       <c r="A37" s="2">
         <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I37" s="2">
         <v>2</v>
       </c>
-      <c r="J37" s="13"/>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" ht="128.5" spans="1:10">
       <c r="A38" s="2">
         <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2805,17 +2804,17 @@
       <c r="I38" s="2">
         <v>2</v>
       </c>
-      <c r="J38" s="13"/>
+      <c r="J38" s="10"/>
     </row>
     <row r="39" ht="60.5" customHeight="1" spans="1:10">
       <c r="A39" s="2">
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>94</v>
+        <v>82</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2827,53 +2826,53 @@
       <c r="I39" s="2">
         <v>2</v>
       </c>
-      <c r="J39" s="13"/>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="10"/>
+      <c r="C40" s="6"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" ht="34" spans="1:10">
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="10"/>
+      <c r="C41" s="6"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-    </row>
-    <row r="42" ht="34" spans="1:10">
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="11"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
+      <c r="J42" s="10"/>
     </row>
     <row r="43" ht="114" spans="1:10">
       <c r="A43" s="2">
         <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2885,39 +2884,39 @@
       <c r="I43" s="2">
         <v>2</v>
       </c>
-      <c r="J43" s="13"/>
+      <c r="J43" s="10"/>
     </row>
     <row r="44" ht="135.5" spans="1:10">
       <c r="A44" s="2">
         <v>25</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I44" s="2">
         <v>2</v>
       </c>
-      <c r="J44" s="13"/>
+      <c r="J44" s="10"/>
     </row>
     <row r="45" ht="80" spans="1:10">
       <c r="A45" s="2">
         <v>26</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -2929,39 +2928,39 @@
       <c r="I45" s="2">
         <v>2</v>
       </c>
-      <c r="J45" s="13"/>
+      <c r="J45" s="10"/>
     </row>
     <row r="46" ht="114" spans="1:10">
       <c r="A46" s="2">
         <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
       </c>
-      <c r="J46" s="13"/>
+      <c r="J46" s="10"/>
     </row>
     <row r="47" ht="131" spans="1:10">
       <c r="A47" s="2">
         <v>28</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2973,39 +2972,39 @@
       <c r="I47" s="2">
         <v>2</v>
       </c>
-      <c r="J47" s="13"/>
+      <c r="J47" s="10"/>
     </row>
     <row r="48" ht="164.5" spans="1:10">
       <c r="A48" s="2">
         <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I48" s="2">
         <v>2</v>
       </c>
-      <c r="J48" s="13"/>
+      <c r="J48" s="10"/>
     </row>
     <row r="49" ht="111.5" spans="1:10">
       <c r="A49" s="2">
         <v>30</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -3017,11 +3016,11 @@
       <c r="I49" s="2">
         <v>2</v>
       </c>
-      <c r="J49" s="13"/>
+      <c r="J49" s="10"/>
     </row>
     <row r="50" ht="17" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3031,23 +3030,23 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
+      <c r="J50" s="10"/>
     </row>
     <row r="51" ht="116" spans="1:10">
       <c r="A51" s="2">
         <v>31</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3057,23 +3056,23 @@
       <c r="I51" s="2">
         <v>1</v>
       </c>
-      <c r="J51" s="13"/>
+      <c r="J51" s="10"/>
     </row>
     <row r="52" ht="114" spans="1:10">
       <c r="A52" s="2">
         <v>32</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3083,23 +3082,23 @@
       <c r="I52" s="2">
         <v>1</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="10"/>
     </row>
     <row r="53" ht="89.5" spans="1:10">
       <c r="A53" s="2">
         <v>33</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -3109,23 +3108,23 @@
       <c r="I53" s="2">
         <v>1</v>
       </c>
-      <c r="J53" s="13"/>
+      <c r="J53" s="10"/>
     </row>
     <row r="54" ht="63" spans="1:10">
       <c r="A54" s="2">
         <v>34</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3135,23 +3134,23 @@
       <c r="I54" s="2">
         <v>1</v>
       </c>
-      <c r="J54" s="13"/>
+      <c r="J54" s="10"/>
     </row>
     <row r="55" ht="217.5" spans="1:10">
       <c r="A55" s="2">
         <v>35</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3161,23 +3160,23 @@
       <c r="I55" s="2">
         <v>1</v>
       </c>
-      <c r="J55" s="13"/>
+      <c r="J55" s="10"/>
     </row>
     <row r="56" ht="167" spans="1:10">
       <c r="A56" s="2">
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3187,23 +3186,23 @@
       <c r="I56" s="2">
         <v>1</v>
       </c>
-      <c r="J56" s="13"/>
+      <c r="J56" s="10"/>
     </row>
     <row r="57" ht="177" spans="1:10">
       <c r="A57" s="2">
         <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3213,23 +3212,23 @@
       <c r="I57" s="2">
         <v>1</v>
       </c>
-      <c r="J57" s="13"/>
+      <c r="J57" s="10"/>
     </row>
     <row r="58" ht="92" spans="1:10">
       <c r="A58" s="2">
         <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3239,23 +3238,23 @@
       <c r="I58" s="2">
         <v>1</v>
       </c>
-      <c r="J58" s="13"/>
+      <c r="J58" s="10"/>
     </row>
     <row r="59" ht="89.5" spans="1:10">
       <c r="A59" s="2">
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -3265,23 +3264,23 @@
       <c r="I59" s="2">
         <v>1</v>
       </c>
-      <c r="J59" s="13"/>
+      <c r="J59" s="10"/>
     </row>
     <row r="60" ht="75" spans="1:10">
       <c r="A60" s="2">
         <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3291,11 +3290,11 @@
       <c r="I60" s="2">
         <v>1</v>
       </c>
-      <c r="J60" s="13"/>
+      <c r="J60" s="10"/>
     </row>
     <row r="61" ht="17" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3305,30 +3304,30 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="13"/>
+      <c r="J61" s="10"/>
     </row>
     <row r="62" ht="87" spans="1:10">
       <c r="A62" s="2">
         <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="12" t="s">
-        <v>120</v>
+      <c r="H62" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I62" s="2">
         <v>10</v>
       </c>
-      <c r="J62" s="13" t="s">
-        <v>121</v>
+      <c r="J62" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="63" ht="119" spans="1:10">
@@ -3336,28 +3335,28 @@
         <v>42</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="12" t="s">
-        <v>123</v>
+      <c r="H63" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="I63" s="2">
         <v>10</v>
       </c>
-      <c r="J63" s="13" t="s">
-        <v>124</v>
+      <c r="J63" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="64" ht="17" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3367,30 +3366,30 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="13"/>
+      <c r="J64" s="10"/>
     </row>
     <row r="65" ht="409.5" spans="1:10">
       <c r="A65" s="2">
         <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="12" t="s">
-        <v>127</v>
+      <c r="H65" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="I65" s="2">
         <v>10</v>
       </c>
-      <c r="J65" s="13" t="s">
-        <v>128</v>
+      <c r="J65" s="10" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
